--- a/Project/DiceWarrior/LubanTool/Datas/__enums__.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/__enums__.xlsx
@@ -1143,7 +1143,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1406,6 +1406,102 @@
         <v>46</v>
       </c>
     </row>
+    <row r="16" spans="1:10">
+      <c r="A16"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>eventcard.EEventCardType</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>中立事件</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>中立事件</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>宝箱事件</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>宝箱事件</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G1:K1"/>

--- a/Project/DiceWarrior/LubanTool/Datas/__enums__.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/__enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24590" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -168,6 +168,58 @@
   </si>
   <si>
     <t>英文</t>
+  </si>
+  <si>
+    <t>eventcard.EEventCardType</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Battle</t>
+  </si>
+  <si>
+    <t>战斗</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>中立事件</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Treasure</t>
+  </si>
+  <si>
+    <t>宝箱事件</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Spite</t>
+  </si>
+  <si>
+    <t>恶意事件</t>
+  </si>
+  <si>
+    <t>Friend</t>
+  </si>
+  <si>
+    <t>友好事件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Special
+</t>
+  </si>
+  <si>
+    <t>特殊事件</t>
   </si>
 </sst>
 </file>
@@ -180,14 +232,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,7 +385,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,12 +563,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,163 +705,169 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1143,363 +1188,362 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="4" width="14.125" customWidth="1"/>
-    <col min="5" max="5" width="9.375" customWidth="1"/>
-    <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="16.25" customWidth="1"/>
-    <col min="9" max="9" width="12.125" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="22.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="99" customHeight="1" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="2:10">
-      <c r="B4" t="s">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>1</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="7:10">
-      <c r="G5" t="s">
+    <row r="5" spans="1:11">
+      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>2</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="7:10">
-      <c r="G6" t="s">
+    <row r="6" spans="1:11">
+      <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>3</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="7:10">
-      <c r="G7" t="s">
+    <row r="7" spans="1:11">
+      <c r="G7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>4</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="7:10">
-      <c r="G8" t="s">
+    <row r="8" spans="1:11">
+      <c r="G8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>5</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
+    <row r="9" spans="1:11">
+      <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="b">
+      <c r="C9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="7:9">
-      <c r="G10" t="s">
+    <row r="10" spans="1:11">
+      <c r="G10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="7:9">
-      <c r="G11" t="s">
+    <row r="11" spans="1:11">
+      <c r="G11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="7:9">
-      <c r="G12" t="s">
+    <row r="12" spans="1:11">
+      <c r="G12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="7:10">
-      <c r="G13" t="s">
+    <row r="13" spans="1:11">
+      <c r="G13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
-      <c r="B14" t="s">
+    <row r="14" spans="1:11">
+      <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="b">
+      <c r="C14" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D14" t="b">
+      <c r="D14" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="7:10">
-      <c r="G15" t="s">
+    <row r="15" spans="1:11">
+      <c r="G15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>2</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>eventcard.EEventCardType</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Battle</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>战斗</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>战斗</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>中立事件</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>中立事件</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Treasure</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>宝箱事件</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>宝箱事件</t>
-        </is>
+    <row r="16" spans="1:11">
+      <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10">
+      <c r="G17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10">
+      <c r="G18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10">
+      <c r="G19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10">
+      <c r="G20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="7:10">
+      <c r="G21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" s="1">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
